--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452326</v>
+        <v>123452327</v>
       </c>
       <c r="B2" t="n">
-        <v>94781</v>
+        <v>98376</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385794</v>
+        <v>385810</v>
       </c>
       <c r="R2" t="n">
-        <v>6441201</v>
+        <v>6441249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452327</v>
+        <v>123452334</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385810</v>
+        <v>385863</v>
       </c>
       <c r="R3" t="n">
-        <v>6441249</v>
+        <v>6441376</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452330</v>
+        <v>123452325</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385804</v>
+        <v>385909</v>
       </c>
       <c r="R4" t="n">
-        <v>6441261</v>
+        <v>6441258</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,7 +1011,7 @@
         <v>123452324</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452334</v>
+        <v>123452333</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385863</v>
+        <v>385913</v>
       </c>
       <c r="R6" t="n">
-        <v>6441376</v>
+        <v>6441281</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452325</v>
+        <v>123452331</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385909</v>
+        <v>385855</v>
       </c>
       <c r="R7" t="n">
-        <v>6441258</v>
+        <v>6441135</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452329</v>
+        <v>123452330</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385813</v>
+        <v>385804</v>
       </c>
       <c r="R8" t="n">
-        <v>6441337</v>
+        <v>6441261</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452328</v>
+        <v>123452332</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385791</v>
+        <v>385907</v>
       </c>
       <c r="R9" t="n">
-        <v>6441358</v>
+        <v>6441260</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452331</v>
+        <v>123452326</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>94787</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385855</v>
+        <v>385794</v>
       </c>
       <c r="R10" t="n">
-        <v>6441135</v>
+        <v>6441201</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452333</v>
+        <v>123452329</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385913</v>
+        <v>385813</v>
       </c>
       <c r="R11" t="n">
-        <v>6441281</v>
+        <v>6441337</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452332</v>
+        <v>123452328</v>
       </c>
       <c r="B12" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385907</v>
+        <v>385791</v>
       </c>
       <c r="R12" t="n">
-        <v>6441260</v>
+        <v>6441358</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452334</v>
+        <v>123452328</v>
       </c>
       <c r="B5" t="n">
         <v>98379</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385863</v>
+        <v>385791</v>
       </c>
       <c r="R5" t="n">
-        <v>6441376</v>
+        <v>6441358</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452328</v>
+        <v>123452334</v>
       </c>
       <c r="B6" t="n">
         <v>98379</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385791</v>
+        <v>385863</v>
       </c>
       <c r="R6" t="n">
-        <v>6441358</v>
+        <v>6441376</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452329</v>
+        <v>123452326</v>
       </c>
       <c r="B2" t="n">
-        <v>98379</v>
+        <v>94807</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385813</v>
+        <v>385794</v>
       </c>
       <c r="R2" t="n">
-        <v>6441337</v>
+        <v>6441201</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452330</v>
+        <v>123452325</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385804</v>
+        <v>385909</v>
       </c>
       <c r="R3" t="n">
-        <v>6441261</v>
+        <v>6441258</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452331</v>
+        <v>123452330</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385855</v>
+        <v>385804</v>
       </c>
       <c r="R4" t="n">
-        <v>6441135</v>
+        <v>6441261</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452328</v>
+        <v>123452324</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385791</v>
+        <v>385852</v>
       </c>
       <c r="R5" t="n">
-        <v>6441358</v>
+        <v>6441306</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1122,7 +1122,7 @@
         <v>123452334</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452324</v>
+        <v>123452328</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385852</v>
+        <v>385791</v>
       </c>
       <c r="R7" t="n">
-        <v>6441306</v>
+        <v>6441358</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452327</v>
+        <v>123452332</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385810</v>
+        <v>385907</v>
       </c>
       <c r="R8" t="n">
-        <v>6441249</v>
+        <v>6441260</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452332</v>
+        <v>123452329</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385907</v>
+        <v>385813</v>
       </c>
       <c r="R9" t="n">
-        <v>6441260</v>
+        <v>6441337</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452325</v>
+        <v>123452327</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385909</v>
+        <v>385810</v>
       </c>
       <c r="R10" t="n">
-        <v>6441258</v>
+        <v>6441249</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452326</v>
+        <v>123452333</v>
       </c>
       <c r="B11" t="n">
-        <v>94790</v>
+        <v>98396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385794</v>
+        <v>385913</v>
       </c>
       <c r="R11" t="n">
-        <v>6441201</v>
+        <v>6441281</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452333</v>
+        <v>123452331</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385913</v>
+        <v>385855</v>
       </c>
       <c r="R12" t="n">
-        <v>6441281</v>
+        <v>6441135</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452326</v>
+        <v>123452330</v>
       </c>
       <c r="B2" t="n">
-        <v>94807</v>
+        <v>98502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385794</v>
+        <v>385804</v>
       </c>
       <c r="R2" t="n">
-        <v>6441201</v>
+        <v>6441261</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452325</v>
+        <v>123452326</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>94813</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385909</v>
+        <v>385794</v>
       </c>
       <c r="R3" t="n">
-        <v>6441258</v>
+        <v>6441201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452330</v>
+        <v>123452329</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385804</v>
+        <v>385813</v>
       </c>
       <c r="R4" t="n">
-        <v>6441261</v>
+        <v>6441337</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452324</v>
+        <v>123452325</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385852</v>
+        <v>385909</v>
       </c>
       <c r="R5" t="n">
-        <v>6441306</v>
+        <v>6441258</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>123452334</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452328</v>
+        <v>123452331</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385791</v>
+        <v>385855</v>
       </c>
       <c r="R7" t="n">
-        <v>6441358</v>
+        <v>6441135</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452332</v>
+        <v>123452327</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385907</v>
+        <v>385810</v>
       </c>
       <c r="R8" t="n">
-        <v>6441260</v>
+        <v>6441249</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452329</v>
+        <v>123452328</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385813</v>
+        <v>385791</v>
       </c>
       <c r="R9" t="n">
-        <v>6441337</v>
+        <v>6441358</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452327</v>
+        <v>123452332</v>
       </c>
       <c r="B10" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385810</v>
+        <v>385907</v>
       </c>
       <c r="R10" t="n">
-        <v>6441249</v>
+        <v>6441260</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1677,7 +1677,7 @@
         <v>123452333</v>
       </c>
       <c r="B11" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452331</v>
+        <v>123452324</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385855</v>
+        <v>385852</v>
       </c>
       <c r="R12" t="n">
-        <v>6441135</v>
+        <v>6441306</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452330</v>
+        <v>123452333</v>
       </c>
       <c r="B2" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385804</v>
+        <v>385913</v>
       </c>
       <c r="R2" t="n">
-        <v>6441261</v>
+        <v>6441281</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452326</v>
+        <v>123452331</v>
       </c>
       <c r="B3" t="n">
-        <v>94813</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385794</v>
+        <v>385855</v>
       </c>
       <c r="R3" t="n">
-        <v>6441201</v>
+        <v>6441135</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452329</v>
+        <v>123452327</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385813</v>
+        <v>385810</v>
       </c>
       <c r="R4" t="n">
-        <v>6441337</v>
+        <v>6441249</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452325</v>
+        <v>123452329</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385909</v>
+        <v>385813</v>
       </c>
       <c r="R5" t="n">
-        <v>6441258</v>
+        <v>6441337</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452334</v>
+        <v>123452326</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>94815</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385863</v>
+        <v>385794</v>
       </c>
       <c r="R6" t="n">
-        <v>6441376</v>
+        <v>6441201</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452331</v>
+        <v>123452330</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385855</v>
+        <v>385804</v>
       </c>
       <c r="R7" t="n">
-        <v>6441135</v>
+        <v>6441261</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452327</v>
+        <v>123452328</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385810</v>
+        <v>385791</v>
       </c>
       <c r="R8" t="n">
-        <v>6441249</v>
+        <v>6441358</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452328</v>
+        <v>123452324</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385791</v>
+        <v>385852</v>
       </c>
       <c r="R9" t="n">
-        <v>6441358</v>
+        <v>6441306</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1566,7 +1566,7 @@
         <v>123452332</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452333</v>
+        <v>123452325</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385913</v>
+        <v>385909</v>
       </c>
       <c r="R11" t="n">
-        <v>6441281</v>
+        <v>6441258</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452324</v>
+        <v>123452334</v>
       </c>
       <c r="B12" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385852</v>
+        <v>385863</v>
       </c>
       <c r="R12" t="n">
-        <v>6441306</v>
+        <v>6441376</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452333</v>
+        <v>123452326</v>
       </c>
       <c r="B2" t="n">
-        <v>98504</v>
+        <v>95323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385913</v>
+        <v>385794</v>
       </c>
       <c r="R2" t="n">
-        <v>6441281</v>
+        <v>6441201</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452331</v>
+        <v>123452327</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385855</v>
+        <v>385810</v>
       </c>
       <c r="R3" t="n">
-        <v>6441135</v>
+        <v>6441249</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452327</v>
+        <v>123452334</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385810</v>
+        <v>385863</v>
       </c>
       <c r="R4" t="n">
-        <v>6441249</v>
+        <v>6441376</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452329</v>
+        <v>123452324</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385813</v>
+        <v>385852</v>
       </c>
       <c r="R5" t="n">
-        <v>6441337</v>
+        <v>6441306</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452326</v>
+        <v>123452328</v>
       </c>
       <c r="B6" t="n">
-        <v>94815</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385794</v>
+        <v>385791</v>
       </c>
       <c r="R6" t="n">
-        <v>6441201</v>
+        <v>6441358</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452330</v>
+        <v>123452325</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385804</v>
+        <v>385909</v>
       </c>
       <c r="R7" t="n">
-        <v>6441261</v>
+        <v>6441258</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452328</v>
+        <v>123452332</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385791</v>
+        <v>385907</v>
       </c>
       <c r="R8" t="n">
-        <v>6441358</v>
+        <v>6441260</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452324</v>
+        <v>123452329</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385852</v>
+        <v>385813</v>
       </c>
       <c r="R9" t="n">
-        <v>6441306</v>
+        <v>6441337</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452332</v>
+        <v>123452330</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385907</v>
+        <v>385804</v>
       </c>
       <c r="R10" t="n">
-        <v>6441260</v>
+        <v>6441261</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452325</v>
+        <v>123452333</v>
       </c>
       <c r="B11" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385909</v>
+        <v>385913</v>
       </c>
       <c r="R11" t="n">
-        <v>6441258</v>
+        <v>6441281</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452334</v>
+        <v>123452331</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385863</v>
+        <v>385855</v>
       </c>
       <c r="R12" t="n">
-        <v>6441376</v>
+        <v>6441135</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452326</v>
+        <v>123452325</v>
       </c>
       <c r="B2" t="n">
-        <v>95323</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385794</v>
+        <v>385909</v>
       </c>
       <c r="R2" t="n">
-        <v>6441201</v>
+        <v>6441258</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452327</v>
+        <v>123452329</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -830,13 +830,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385810</v>
+        <v>385813</v>
       </c>
       <c r="R3" t="n">
-        <v>6441249</v>
+        <v>6441337</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452334</v>
+        <v>123452324</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385863</v>
+        <v>385852</v>
       </c>
       <c r="R4" t="n">
-        <v>6441376</v>
+        <v>6441306</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452324</v>
+        <v>123452333</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1052,13 +1052,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385852</v>
+        <v>385913</v>
       </c>
       <c r="R5" t="n">
-        <v>6441306</v>
+        <v>6441281</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452328</v>
+        <v>123452327</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385791</v>
+        <v>385810</v>
       </c>
       <c r="R6" t="n">
-        <v>6441358</v>
+        <v>6441249</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452325</v>
+        <v>123452326</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385909</v>
+        <v>385794</v>
       </c>
       <c r="R7" t="n">
-        <v>6441258</v>
+        <v>6441201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452332</v>
+        <v>123452331</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385907</v>
+        <v>385855</v>
       </c>
       <c r="R8" t="n">
-        <v>6441260</v>
+        <v>6441135</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452329</v>
+        <v>123452328</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385813</v>
+        <v>385791</v>
       </c>
       <c r="R9" t="n">
-        <v>6441337</v>
+        <v>6441358</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452330</v>
+        <v>123452334</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385804</v>
+        <v>385863</v>
       </c>
       <c r="R10" t="n">
-        <v>6441261</v>
+        <v>6441376</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452333</v>
+        <v>123452330</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385913</v>
+        <v>385804</v>
       </c>
       <c r="R11" t="n">
-        <v>6441281</v>
+        <v>6441261</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452331</v>
+        <v>123452332</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385855</v>
+        <v>385907</v>
       </c>
       <c r="R12" t="n">
-        <v>6441135</v>
+        <v>6441260</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452325</v>
+        <v>123452330</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385909</v>
+        <v>385804</v>
       </c>
       <c r="R2" t="n">
-        <v>6441258</v>
+        <v>6441261</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452324</v>
+        <v>123452327</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385852</v>
+        <v>385810</v>
       </c>
       <c r="R4" t="n">
-        <v>6441306</v>
+        <v>6441249</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452333</v>
+        <v>123452331</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385913</v>
+        <v>385855</v>
       </c>
       <c r="R5" t="n">
-        <v>6441281</v>
+        <v>6441135</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452327</v>
+        <v>123452333</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385810</v>
+        <v>385913</v>
       </c>
       <c r="R6" t="n">
-        <v>6441249</v>
+        <v>6441281</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452326</v>
+        <v>123452334</v>
       </c>
       <c r="B7" t="n">
-        <v>95323</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385794</v>
+        <v>385863</v>
       </c>
       <c r="R7" t="n">
-        <v>6441201</v>
+        <v>6441376</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452331</v>
+        <v>123452332</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385855</v>
+        <v>385907</v>
       </c>
       <c r="R8" t="n">
-        <v>6441135</v>
+        <v>6441260</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452328</v>
+        <v>123452326</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385791</v>
+        <v>385794</v>
       </c>
       <c r="R9" t="n">
-        <v>6441358</v>
+        <v>6441201</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452334</v>
+        <v>123452324</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1607,13 +1607,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385863</v>
+        <v>385852</v>
       </c>
       <c r="R10" t="n">
-        <v>6441376</v>
+        <v>6441306</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452330</v>
+        <v>123452328</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385804</v>
+        <v>385791</v>
       </c>
       <c r="R11" t="n">
-        <v>6441261</v>
+        <v>6441358</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452332</v>
+        <v>123452325</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385907</v>
+        <v>385909</v>
       </c>
       <c r="R12" t="n">
-        <v>6441260</v>
+        <v>6441258</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452330</v>
+        <v>123452325</v>
       </c>
       <c r="B2" t="n">
         <v>98079</v>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385804</v>
+        <v>385909</v>
       </c>
       <c r="R2" t="n">
-        <v>6441261</v>
+        <v>6441258</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452329</v>
+        <v>123452331</v>
       </c>
       <c r="B3" t="n">
         <v>98079</v>
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385813</v>
+        <v>385855</v>
       </c>
       <c r="R3" t="n">
-        <v>6441337</v>
+        <v>6441135</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452327</v>
+        <v>123452334</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385810</v>
+        <v>385863</v>
       </c>
       <c r="R4" t="n">
-        <v>6441249</v>
+        <v>6441376</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123452331</v>
+        <v>123452332</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385855</v>
+        <v>385907</v>
       </c>
       <c r="R5" t="n">
-        <v>6441135</v>
+        <v>6441260</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452333</v>
+        <v>123452326</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>95323</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385913</v>
+        <v>385794</v>
       </c>
       <c r="R6" t="n">
-        <v>6441281</v>
+        <v>6441201</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452334</v>
+        <v>123452328</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385863</v>
+        <v>385791</v>
       </c>
       <c r="R7" t="n">
-        <v>6441376</v>
+        <v>6441358</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452332</v>
+        <v>123452327</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385907</v>
+        <v>385810</v>
       </c>
       <c r="R8" t="n">
-        <v>6441260</v>
+        <v>6441249</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452326</v>
+        <v>123452329</v>
       </c>
       <c r="B9" t="n">
-        <v>95323</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385794</v>
+        <v>385813</v>
       </c>
       <c r="R9" t="n">
-        <v>6441201</v>
+        <v>6441337</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452328</v>
+        <v>123452333</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385791</v>
+        <v>385913</v>
       </c>
       <c r="R11" t="n">
-        <v>6441358</v>
+        <v>6441281</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452325</v>
+        <v>123452330</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1829,13 +1829,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385909</v>
+        <v>385804</v>
       </c>
       <c r="R12" t="n">
-        <v>6441258</v>
+        <v>6441261</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,12 +1859,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123452328</v>
+        <v>123452326</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385791</v>
+        <v>385794</v>
       </c>
       <c r="R2" t="n">
-        <v>6441358</v>
+        <v>6441201</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123452334</v>
+        <v>123452324</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385863</v>
+        <v>385852</v>
       </c>
       <c r="R3" t="n">
-        <v>6441376</v>
+        <v>6441306</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123452332</v>
+        <v>123452325</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385907</v>
+        <v>385909</v>
       </c>
       <c r="R4" t="n">
-        <v>6441260</v>
+        <v>6441258</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,12 +996,7 @@
         <v>123452327</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123452324</v>
+        <v>123452328</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,13 +1138,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385852</v>
+        <v>385791</v>
       </c>
       <c r="R6" t="n">
-        <v>6441306</v>
+        <v>6441358</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1168,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1230,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123452331</v>
+        <v>123452329</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385855</v>
+        <v>385813</v>
       </c>
       <c r="R7" t="n">
-        <v>6441135</v>
+        <v>6441337</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1341,15 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123452329</v>
+        <v>123452330</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385813</v>
+        <v>385804</v>
       </c>
       <c r="R8" t="n">
-        <v>6441337</v>
+        <v>6441261</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1452,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123452325</v>
+        <v>123452331</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1496,13 +1456,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385909</v>
+        <v>385855</v>
       </c>
       <c r="R9" t="n">
-        <v>6441258</v>
+        <v>6441135</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,12 +1486,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123452326</v>
+        <v>123452332</v>
       </c>
       <c r="B10" t="n">
-        <v>95345</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,13 +1562,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385794</v>
+        <v>385907</v>
       </c>
       <c r="R10" t="n">
-        <v>6441201</v>
+        <v>6441260</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1637,12 +1592,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,15 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123452330</v>
+        <v>123452333</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385804</v>
+        <v>385913</v>
       </c>
       <c r="R11" t="n">
-        <v>6441261</v>
+        <v>6441281</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1785,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123452333</v>
+        <v>123452334</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385913</v>
+        <v>385863</v>
       </c>
       <c r="R12" t="n">
-        <v>6441281</v>
+        <v>6441376</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 22884-2023 artfynd.xlsx
+++ b/artfynd/A 22884-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452326</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452324</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452325</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452327</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452328</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452329</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452330</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452331</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452332</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452333</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,8 +1893,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123452334</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>